--- a/VerveStacks_ARE_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ARE_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7DE08F7-53D4-4DBF-B870-22E86824E4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF47F524-650F-440D-84E1-02CCD017F0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2674,7 +2674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57BE008B-B22F-450E-927F-9E06D328F3C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A54A93-9C9D-4865-8DEE-52F3D3ABB583}">
   <dimension ref="B2:AF312"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9981,7 +9981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D42165C-9A30-4355-8481-CFFA5BCD4423}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC97642-E730-41A9-B68F-2A591AD25921}">
   <dimension ref="B9:L12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ARE_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ARE_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF47F524-650F-440D-84E1-02CCD017F0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85D901F2-57A7-440D-BF3F-640133334E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2674,7 +2674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A54A93-9C9D-4865-8DEE-52F3D3ABB583}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF49E80-05A3-4DCF-81F8-431AA0C19EDA}">
   <dimension ref="B2:AF312"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9981,7 +9981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC97642-E730-41A9-B68F-2A591AD25921}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84414F06-A995-4696-BEE9-4C7482D36ED8}">
   <dimension ref="B9:L12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ARE_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ARE_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85D901F2-57A7-440D-BF3F-640133334E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF9F8333-1EBA-47AC-976E-CF79CDDED1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2674,7 +2674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF49E80-05A3-4DCF-81F8-431AA0C19EDA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94435853-2865-4C30-942C-456ECB912633}">
   <dimension ref="B2:AF312"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9981,7 +9981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84414F06-A995-4696-BEE9-4C7482D36ED8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB66C5EF-4877-44B3-A9E3-5A73F3E01708}">
   <dimension ref="B9:L12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
